--- a/AAII_Financials/Yearly/FBGL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FBGL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>FBGL</t>
   </si>
@@ -1716,7 +1716,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13700</v>
+        <v>10500</v>
       </c>
       <c r="E43" s="3">
         <v>4900</v>
@@ -1781,8 +1781,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>3300</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7700</v>
+        <v>8400</v>
       </c>
       <c r="E59" s="3">
         <v>5200</v>
@@ -2906,7 +2906,7 @@
         <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
